--- a/每日输出/初短二部/郑州-初短二部-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/初短二部/郑州-初短二部-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -1514,16 +1514,16 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -1555,16 +1555,16 @@
         <v>3</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="K4" s="3" t="e">
-        <v>#N/A</v>
       </c>
     </row>
     <row r="5">
@@ -1596,16 +1596,16 @@
         <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="e">
-        <v>#N/A</v>
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1633,16 +1633,16 @@
         <v>8</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="e">
-        <v>#N/A</v>
+        <v>0.875</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="7">
@@ -1670,16 +1670,16 @@
         <v>8</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="e">
-        <v>#N/A</v>
+        <v>0.875</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0.2857142857142857</v>
       </c>
     </row>
   </sheetData>
@@ -1696,14 +1696,421 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>无数据</t>
-        </is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>学部</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>年级</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>战队</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>老师邮箱</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>老师姓名</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>个微授权</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>整体正常</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>运营中心</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>小时</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>初短二部</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>以梦为马</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>liumengying</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>刘梦颖</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>郑州二部</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>初短二部</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>以梦为马</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>liuyan01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>刘岩</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>郑州二部</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>初短二部</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>以梦为马</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>songmeixuan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>宋美璇</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>郑州二部</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>初短二部</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>以梦为马</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>zhangyaxue</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>张亚雪</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>郑州二部</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>初短二部</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>长风迎捷</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>changlinjie</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>常琳洁</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>郑州二部</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>初短二部</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>长风迎捷</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>lihaoyi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>李浩毅</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>郑州二部</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>初短二部</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>骏成必燃</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>guojiafa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>郭家发</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>郑州二部</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1782,13 +2189,16 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="3">
@@ -1811,12 +2221,15 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1840,13 +2253,16 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
